--- a/public/templates/en/register.xlsx
+++ b/public/templates/en/register.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -438,36 +438,39 @@
         <v>status</v>
       </c>
       <c r="G1" t="str">
+        <v>runtime_ai</v>
+      </c>
+      <c r="H1" t="str">
         <v>ai_type</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>impact</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>data</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>affected</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>autonomy</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>oversight</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>access</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>reversibility</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>tier</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>deep_dive_complete</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>updatedAt</v>
       </c>
     </row>
@@ -491,36 +494,39 @@
         <v>Status</v>
       </c>
       <c r="G2" t="str">
+        <v>Does the solution use AI when it runs?</v>
+      </c>
+      <c r="H2" t="str">
         <v>AI type</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>What does the AI's output influence?</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>What data does it use?</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>Who could be affected?</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>How much does it act on its own?</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>How is its work reviewed by people?</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>What can it change in other systems?</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>If it gets something wrong, can the result be undone?</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>Risk tier</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>Deep-dive</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>Updated</v>
       </c>
     </row>
@@ -544,36 +550,39 @@
         <v>production</v>
       </c>
       <c r="G3" t="str">
+        <v>yes</v>
+      </c>
+      <c r="H3" t="str">
         <v>generative</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>public-info</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>none</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>public</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>monitored</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>exceptions</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>none</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>easy</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>limited</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>false</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>2026-01-15</v>
       </c>
     </row>
@@ -597,42 +606,45 @@
         <v>pilot</v>
       </c>
       <c r="G4" t="str">
+        <v>yes</v>
+      </c>
+      <c r="H4" t="str">
         <v>agentic</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>recommend-individuals</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>personal</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>public</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>monitored</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>exceptions</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>record</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>easy</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>high</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>false</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="R4" t="str">
         <v>2026-01-15</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/en/register.xlsx
+++ b/public/templates/en/register.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:T4"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -438,39 +438,45 @@
         <v>status</v>
       </c>
       <c r="G1" t="str">
+        <v>product</v>
+      </c>
+      <c r="H1" t="str">
+        <v>deployment</v>
+      </c>
+      <c r="I1" t="str">
         <v>runtime_ai</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>ai_type</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>impact</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>data</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>affected</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>autonomy</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>oversight</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>access</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>reversibility</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>tier</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>deep_dive_complete</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>updatedAt</v>
       </c>
     </row>
@@ -494,39 +500,45 @@
         <v>Status</v>
       </c>
       <c r="G2" t="str">
+        <v>Product</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Deployment</v>
+      </c>
+      <c r="I2" t="str">
         <v>Does the solution use AI when it runs?</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>AI type</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>What does the AI's output influence?</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>What data does it use?</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>Who could be affected?</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>How much does it act on its own?</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>How is its work reviewed by people?</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>What can it change in other systems?</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Q2" t="str">
         <v>If it gets something wrong, can the result be undone?</v>
       </c>
-      <c r="P2" t="str">
+      <c r="R2" t="str">
         <v>Risk tier</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="S2" t="str">
         <v>Deep-dive</v>
       </c>
-      <c r="R2" t="str">
+      <c r="T2" t="str">
         <v>Updated</v>
       </c>
     </row>
@@ -549,40 +561,40 @@
       <c r="F3" t="str">
         <v>production</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>yes</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>generative</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>public-info</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>none</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>public</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
         <v>monitored</v>
       </c>
-      <c r="M3" t="str">
+      <c r="O3" t="str">
         <v>exceptions</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <v>none</v>
       </c>
-      <c r="O3" t="str">
+      <c r="Q3" t="str">
         <v>easy</v>
       </c>
-      <c r="P3" t="str">
+      <c r="R3" t="str">
         <v>limited</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="S3" t="str">
         <v>false</v>
       </c>
-      <c r="R3" t="str">
+      <c r="T3" t="str">
         <v>2026-01-15</v>
       </c>
     </row>
@@ -605,46 +617,46 @@
       <c r="F4" t="str">
         <v>pilot</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>yes</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>agentic</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>recommend-individuals</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>personal</v>
       </c>
-      <c r="K4" t="str">
+      <c r="M4" t="str">
         <v>public</v>
       </c>
-      <c r="L4" t="str">
+      <c r="N4" t="str">
         <v>monitored</v>
       </c>
-      <c r="M4" t="str">
+      <c r="O4" t="str">
         <v>exceptions</v>
       </c>
-      <c r="N4" t="str">
+      <c r="P4" t="str">
         <v>record</v>
       </c>
-      <c r="O4" t="str">
+      <c r="Q4" t="str">
         <v>easy</v>
       </c>
-      <c r="P4" t="str">
+      <c r="R4" t="str">
         <v>high</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="S4" t="str">
         <v>false</v>
       </c>
-      <c r="R4" t="str">
+      <c r="T4" t="str">
         <v>2026-01-15</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T4"/>
   </ignoredErrors>
 </worksheet>
 </file>